--- a/sns-team-training/新人マニュアル_ヒアリングシート_CS_LP_広告.xlsx
+++ b/sns-team-training/新人マニュアル_ヒアリングシート_CS_LP_広告.xlsx
@@ -11,6 +11,7 @@
     <sheet name="CSチーム" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="LPチーム" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="広告チーム" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="媒体リンク・ログイン情報" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -72,8 +73,14 @@
       <color rgb="00548235"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="IPAGothic"/>
+      <b val="1"/>
+      <color rgb="00C0392B"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -105,8 +112,13 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4E4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -128,11 +140,55 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -163,6 +219,12 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -701,6 +763,9 @@
           <t>① チーム概要・役割・目的</t>
         </is>
       </c>
+      <c r="C4" s="12" t="n"/>
+      <c r="D4" s="12" t="n"/>
+      <c r="E4" s="13" t="n"/>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" s="8" t="n">
@@ -756,6 +821,9 @@
           <t>② 使用ツール・環境</t>
         </is>
       </c>
+      <c r="C8" s="12" t="n"/>
+      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="13" t="n"/>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" s="8" t="n">
@@ -811,6 +879,9 @@
           <t>③ 基本用語・前提知識</t>
         </is>
       </c>
+      <c r="C12" s="12" t="n"/>
+      <c r="D12" s="12" t="n"/>
+      <c r="E12" s="13" t="n"/>
     </row>
     <row r="13" ht="38" customHeight="1">
       <c r="B13" s="8" t="n">
@@ -850,6 +921,9 @@
           <t>④ 主要業務フロー（手順）</t>
         </is>
       </c>
+      <c r="C15" s="12" t="n"/>
+      <c r="D15" s="12" t="n"/>
+      <c r="E15" s="13" t="n"/>
     </row>
     <row r="16" ht="38" customHeight="1">
       <c r="B16" s="8" t="n">
@@ -937,6 +1011,9 @@
           <t>⑤ 品質基準・ルール（必ず守る／目安）</t>
         </is>
       </c>
+      <c r="C21" s="12" t="n"/>
+      <c r="D21" s="12" t="n"/>
+      <c r="E21" s="13" t="n"/>
     </row>
     <row r="22" ht="38" customHeight="1">
       <c r="B22" s="8" t="n">
@@ -1008,6 +1085,9 @@
           <t>⑥ よくあるNG・注意点</t>
         </is>
       </c>
+      <c r="C26" s="12" t="n"/>
+      <c r="D26" s="12" t="n"/>
+      <c r="E26" s="13" t="n"/>
     </row>
     <row r="27" ht="38" customHeight="1">
       <c r="B27" s="8" t="n">
@@ -1031,6 +1111,9 @@
           <t>⑦ 数値・KPI・目標</t>
         </is>
       </c>
+      <c r="C28" s="12" t="n"/>
+      <c r="D28" s="12" t="n"/>
+      <c r="E28" s="13" t="n"/>
     </row>
     <row r="29" ht="38" customHeight="1">
       <c r="B29" s="8" t="n">
@@ -1054,6 +1137,9 @@
           <t>⑧ 報連相・社内ルール</t>
         </is>
       </c>
+      <c r="C30" s="12" t="n"/>
+      <c r="D30" s="12" t="n"/>
+      <c r="E30" s="13" t="n"/>
     </row>
     <row r="31" ht="38" customHeight="1">
       <c r="B31" s="8" t="n">
@@ -1093,6 +1179,9 @@
           <t>⑨ 独り立ちの定義</t>
         </is>
       </c>
+      <c r="C33" s="12" t="n"/>
+      <c r="D33" s="12" t="n"/>
+      <c r="E33" s="13" t="n"/>
     </row>
     <row r="34" ht="38" customHeight="1">
       <c r="B34" s="8" t="n">
@@ -1116,6 +1205,9 @@
           <t>⑩ 参考資料・確認場所</t>
         </is>
       </c>
+      <c r="C35" s="12" t="n"/>
+      <c r="D35" s="12" t="n"/>
+      <c r="E35" s="13" t="n"/>
     </row>
     <row r="36" ht="38" customHeight="1">
       <c r="B36" s="8" t="n">
@@ -1210,6 +1302,9 @@
           <t>① チーム概要・役割・目的</t>
         </is>
       </c>
+      <c r="C4" s="12" t="n"/>
+      <c r="D4" s="12" t="n"/>
+      <c r="E4" s="13" t="n"/>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" s="8" t="n">
@@ -1265,6 +1360,9 @@
           <t>② 使用ツール・環境</t>
         </is>
       </c>
+      <c r="C8" s="12" t="n"/>
+      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="13" t="n"/>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" s="8" t="n">
@@ -1320,6 +1418,9 @@
           <t>③ 基本用語・前提知識</t>
         </is>
       </c>
+      <c r="C12" s="12" t="n"/>
+      <c r="D12" s="12" t="n"/>
+      <c r="E12" s="13" t="n"/>
     </row>
     <row r="13" ht="38" customHeight="1">
       <c r="B13" s="8" t="n">
@@ -1359,6 +1460,9 @@
           <t>④ 主要業務フロー（手順）</t>
         </is>
       </c>
+      <c r="C15" s="12" t="n"/>
+      <c r="D15" s="12" t="n"/>
+      <c r="E15" s="13" t="n"/>
     </row>
     <row r="16" ht="38" customHeight="1">
       <c r="B16" s="8" t="n">
@@ -1446,6 +1550,9 @@
           <t>⑤ 品質基準・ルール（必ず守る／目安）</t>
         </is>
       </c>
+      <c r="C21" s="12" t="n"/>
+      <c r="D21" s="12" t="n"/>
+      <c r="E21" s="13" t="n"/>
     </row>
     <row r="22" ht="38" customHeight="1">
       <c r="B22" s="8" t="n">
@@ -1501,6 +1608,9 @@
           <t>⑥ よくあるNG・注意点</t>
         </is>
       </c>
+      <c r="C25" s="12" t="n"/>
+      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="13" t="n"/>
     </row>
     <row r="26" ht="38" customHeight="1">
       <c r="B26" s="8" t="n">
@@ -1524,6 +1634,9 @@
           <t>⑦ 数値・KPI・目標</t>
         </is>
       </c>
+      <c r="C27" s="12" t="n"/>
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="13" t="n"/>
     </row>
     <row r="28" ht="38" customHeight="1">
       <c r="B28" s="8" t="n">
@@ -1547,6 +1660,9 @@
           <t>⑧ 報連相・社内ルール</t>
         </is>
       </c>
+      <c r="C29" s="12" t="n"/>
+      <c r="D29" s="12" t="n"/>
+      <c r="E29" s="13" t="n"/>
     </row>
     <row r="30" ht="38" customHeight="1">
       <c r="B30" s="8" t="n">
@@ -1570,6 +1686,9 @@
           <t>⑨ 独り立ちの定義</t>
         </is>
       </c>
+      <c r="C31" s="12" t="n"/>
+      <c r="D31" s="12" t="n"/>
+      <c r="E31" s="13" t="n"/>
     </row>
     <row r="32" ht="38" customHeight="1">
       <c r="B32" s="8" t="n">
@@ -1593,6 +1712,9 @@
           <t>⑩ 参考資料・確認場所</t>
         </is>
       </c>
+      <c r="C33" s="12" t="n"/>
+      <c r="D33" s="12" t="n"/>
+      <c r="E33" s="13" t="n"/>
     </row>
     <row r="34" ht="38" customHeight="1">
       <c r="B34" s="8" t="n">
@@ -1687,6 +1809,9 @@
           <t>① チーム概要・役割・目的</t>
         </is>
       </c>
+      <c r="C4" s="12" t="n"/>
+      <c r="D4" s="12" t="n"/>
+      <c r="E4" s="13" t="n"/>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" s="8" t="n">
@@ -1742,6 +1867,9 @@
           <t>② 使用ツール・環境</t>
         </is>
       </c>
+      <c r="C8" s="12" t="n"/>
+      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="13" t="n"/>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" s="8" t="n">
@@ -1797,6 +1925,9 @@
           <t>③ 基本用語・前提知識</t>
         </is>
       </c>
+      <c r="C12" s="12" t="n"/>
+      <c r="D12" s="12" t="n"/>
+      <c r="E12" s="13" t="n"/>
     </row>
     <row r="13" ht="38" customHeight="1">
       <c r="B13" s="8" t="n">
@@ -1836,6 +1967,9 @@
           <t>④ 主要業務フロー（手順）</t>
         </is>
       </c>
+      <c r="C15" s="12" t="n"/>
+      <c r="D15" s="12" t="n"/>
+      <c r="E15" s="13" t="n"/>
     </row>
     <row r="16" ht="38" customHeight="1">
       <c r="B16" s="8" t="n">
@@ -1939,6 +2073,9 @@
           <t>⑤ 品質基準・ルール（必ず守る／目安）</t>
         </is>
       </c>
+      <c r="C22" s="12" t="n"/>
+      <c r="D22" s="12" t="n"/>
+      <c r="E22" s="13" t="n"/>
     </row>
     <row r="23" ht="38" customHeight="1">
       <c r="B23" s="8" t="n">
@@ -1994,6 +2131,9 @@
           <t>⑥ よくあるNG・注意点</t>
         </is>
       </c>
+      <c r="C26" s="12" t="n"/>
+      <c r="D26" s="12" t="n"/>
+      <c r="E26" s="13" t="n"/>
     </row>
     <row r="27" ht="38" customHeight="1">
       <c r="B27" s="8" t="n">
@@ -2017,6 +2157,9 @@
           <t>⑦ 数値・KPI・目標</t>
         </is>
       </c>
+      <c r="C28" s="12" t="n"/>
+      <c r="D28" s="12" t="n"/>
+      <c r="E28" s="13" t="n"/>
     </row>
     <row r="29" ht="38" customHeight="1">
       <c r="B29" s="8" t="n">
@@ -2040,6 +2183,9 @@
           <t>⑧ 報連相・社内ルール</t>
         </is>
       </c>
+      <c r="C30" s="12" t="n"/>
+      <c r="D30" s="12" t="n"/>
+      <c r="E30" s="13" t="n"/>
     </row>
     <row r="31" ht="38" customHeight="1">
       <c r="B31" s="8" t="n">
@@ -2079,6 +2225,9 @@
           <t>⑨ 独り立ちの定義</t>
         </is>
       </c>
+      <c r="C33" s="12" t="n"/>
+      <c r="D33" s="12" t="n"/>
+      <c r="E33" s="13" t="n"/>
     </row>
     <row r="34" ht="38" customHeight="1">
       <c r="B34" s="8" t="n">
@@ -2102,6 +2251,9 @@
           <t>⑩ 参考資料・確認場所</t>
         </is>
       </c>
+      <c r="C35" s="12" t="n"/>
+      <c r="D35" s="12" t="n"/>
+      <c r="E35" s="13" t="n"/>
     </row>
     <row r="36" ht="38" customHeight="1">
       <c r="B36" s="8" t="n">
@@ -2136,4 +2288,437 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:G34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>媒体リンク・ログイン情報一覧（新人へ事前共有用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>※重要：パスワード/コードは平文でここに書かず、パスワード管理ツール(1Password/Bitwarden等)で管理し安全な方法で共有してください。本シートには『URL・ID・保管場所』の記入を推奨。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>チーム/区分</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>ツール・媒体名</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>ログインURL</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>アカウント/ID(メール等)</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>パスワード/コード(推奨:保管場所を記入)</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>権限・備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>(記入例)</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Meta広告マネージャ</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>https://business.facebook.com/</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>ads@libetee.co.jp</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>1Password『広告』に保管</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>運用担当のみ/編集権限</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="B7" s="15" t="inlineStr"/>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Google Drive</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr"/>
+      <c r="E7" s="10" t="inlineStr"/>
+      <c r="F7" s="10" t="inlineStr"/>
+      <c r="G7" s="10" t="inlineStr"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="B8" s="15" t="inlineStr"/>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Chatwork / Slack</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr"/>
+      <c r="E8" s="10" t="inlineStr"/>
+      <c r="F8" s="10" t="inlineStr"/>
+      <c r="G8" s="10" t="inlineStr"/>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="B9" s="15" t="inlineStr"/>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>楽天RMS(受注・商品)</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr"/>
+      <c r="E9" s="10" t="inlineStr"/>
+      <c r="F9" s="10" t="inlineStr"/>
+      <c r="G9" s="10" t="inlineStr"/>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="B10" s="15" t="inlineStr"/>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>パスワード管理ツール(1Password等)</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr"/>
+      <c r="E10" s="10" t="inlineStr"/>
+      <c r="F10" s="10" t="inlineStr"/>
+      <c r="G10" s="10" t="inlineStr"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>CSチーム</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="B12" s="15" t="inlineStr"/>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>問い合わせ用メール</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr"/>
+      <c r="E12" s="10" t="inlineStr"/>
+      <c r="F12" s="10" t="inlineStr"/>
+      <c r="G12" s="10" t="inlineStr"/>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="B13" s="15" t="inlineStr"/>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>楽天メッセージ/RMS</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr"/>
+      <c r="E13" s="10" t="inlineStr"/>
+      <c r="F13" s="10" t="inlineStr"/>
+      <c r="G13" s="10" t="inlineStr"/>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="B14" s="15" t="inlineStr"/>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>電話/チャット窓口</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr"/>
+      <c r="E14" s="10" t="inlineStr"/>
+      <c r="F14" s="10" t="inlineStr"/>
+      <c r="G14" s="10" t="inlineStr"/>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="B15" s="15" t="inlineStr"/>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>レビュー返信(楽天/IG)</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr"/>
+      <c r="E15" s="10" t="inlineStr"/>
+      <c r="F15" s="10" t="inlineStr"/>
+      <c r="G15" s="10" t="inlineStr"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>LPチーム</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="B17" s="15" t="inlineStr"/>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>LP作成(Shopify/STUDIO等)</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr"/>
+      <c r="E17" s="10" t="inlineStr"/>
+      <c r="F17" s="10" t="inlineStr"/>
+      <c r="G17" s="10" t="inlineStr"/>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="B18" s="15" t="inlineStr"/>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Figma</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr"/>
+      <c r="E18" s="10" t="inlineStr"/>
+      <c r="F18" s="10" t="inlineStr"/>
+      <c r="G18" s="10" t="inlineStr"/>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="B19" s="15" t="inlineStr"/>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Canva</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr"/>
+      <c r="E19" s="10" t="inlineStr"/>
+      <c r="F19" s="10" t="inlineStr"/>
+      <c r="G19" s="10" t="inlineStr"/>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="B20" s="15" t="inlineStr"/>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>GA4(解析)</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr"/>
+      <c r="E20" s="10" t="inlineStr"/>
+      <c r="F20" s="10" t="inlineStr"/>
+      <c r="G20" s="10" t="inlineStr"/>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="B21" s="15" t="inlineStr"/>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>ヒートマップ(Clarity等)</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr"/>
+      <c r="E21" s="10" t="inlineStr"/>
+      <c r="F21" s="10" t="inlineStr"/>
+      <c r="G21" s="10" t="inlineStr"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>広告チーム</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="B23" s="15" t="inlineStr"/>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Meta広告マネージャ</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr"/>
+      <c r="E23" s="10" t="inlineStr"/>
+      <c r="F23" s="10" t="inlineStr"/>
+      <c r="G23" s="10" t="inlineStr"/>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="B24" s="15" t="inlineStr"/>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Google広告(Google Ads)</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr"/>
+      <c r="E24" s="10" t="inlineStr"/>
+      <c r="F24" s="10" t="inlineStr"/>
+      <c r="G24" s="10" t="inlineStr"/>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="B25" s="15" t="inlineStr"/>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>TikTok広告</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr"/>
+      <c r="E25" s="10" t="inlineStr"/>
+      <c r="F25" s="10" t="inlineStr"/>
+      <c r="G25" s="10" t="inlineStr"/>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="B26" s="15" t="inlineStr"/>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>LINE/Yahoo広告</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr"/>
+      <c r="E26" s="10" t="inlineStr"/>
+      <c r="F26" s="10" t="inlineStr"/>
+      <c r="G26" s="10" t="inlineStr"/>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="B27" s="15" t="inlineStr"/>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>GA4/計測</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr"/>
+      <c r="E27" s="10" t="inlineStr"/>
+      <c r="F27" s="10" t="inlineStr"/>
+      <c r="G27" s="10" t="inlineStr"/>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="B28" s="15" t="inlineStr"/>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Metaピクセル/イベント管理</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr"/>
+      <c r="E28" s="10" t="inlineStr"/>
+      <c r="F28" s="10" t="inlineStr"/>
+      <c r="G28" s="10" t="inlineStr"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>SNS(参考)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="B30" s="15" t="inlineStr"/>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Instagram @libetee_travel</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr"/>
+      <c r="E30" s="10" t="inlineStr"/>
+      <c r="F30" s="10" t="inlineStr"/>
+      <c r="G30" s="10" t="inlineStr"/>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="B31" s="15" t="inlineStr"/>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Instagram @libetee_official</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr"/>
+      <c r="E31" s="10" t="inlineStr"/>
+      <c r="F31" s="10" t="inlineStr"/>
+      <c r="G31" s="10" t="inlineStr"/>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="B32" s="15" t="inlineStr"/>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>Instagram @libetee_japan</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr"/>
+      <c r="E32" s="10" t="inlineStr"/>
+      <c r="F32" s="10" t="inlineStr"/>
+      <c r="G32" s="10" t="inlineStr"/>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="B33" s="15" t="inlineStr"/>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Meta Business Suite</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr"/>
+      <c r="E33" s="10" t="inlineStr"/>
+      <c r="F33" s="10" t="inlineStr"/>
+      <c r="G33" s="10" t="inlineStr"/>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="B34" s="15" t="inlineStr"/>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr"/>
+      <c r="E34" s="10" t="inlineStr"/>
+      <c r="F34" s="10" t="inlineStr"/>
+      <c r="G34" s="10" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="B11:G11"/>
+    <mergeCell ref="B6:G6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/sns-team-training/新人マニュアル_ヒアリングシート_CS_LP_広告.xlsx
+++ b/sns-team-training/新人マニュアル_ヒアリングシート_CS_LP_広告.xlsx
@@ -11,7 +11,8 @@
     <sheet name="CSチーム" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="LPチーム" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="広告チーム" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="媒体リンク・ログイン情報" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="報告ルール" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="媒体リンク・ログイン情報" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -79,8 +80,13 @@
       <color rgb="00C0392B"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="IPAGothic"/>
+      <color rgb="00C0392B"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -115,6 +121,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4E4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FBEAE8"/>
       </patternFill>
     </fill>
   </fills>
@@ -188,7 +199,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -225,6 +236,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2296,6 +2316,363 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="B1:F31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>報告ルール（新人が必ず覚える基本＋チーム別設定）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>SNSチームと共通の考え方：報告は『必ず・早めに・文字で残す』。下段の表はチームごとに具体を記入してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>■ 共通の報告ルール（必ず守る・基本）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>・依頼されたタスクが完了したら、必ず『完了報告』をする（言われる前に自分から）。</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="n"/>
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="12" t="n"/>
+      <c r="F5" s="13" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>・進捗・完了は口頭だけでなく、できるだけ文字で残す（チャット等）。</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="13" t="n"/>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>・日次で『今日やったこと／未完了／困っていること』を報告する。</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="n"/>
+      <c r="D7" s="12" t="n"/>
+      <c r="E7" s="12" t="n"/>
+      <c r="F7" s="13" t="n"/>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>・数値・成果は決まった頻度（日次/週次）でレポートする。</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="n"/>
+      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="12" t="n"/>
+      <c r="F8" s="13" t="n"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>・不明点は自己判断で長時間止まらず、早めに相談する。</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="12" t="n"/>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="13" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>・トラブル・異常（クレーム/数値悪化/配信停止 等）は気づいた時点で即共有する。</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="n"/>
+      <c r="D10" s="12" t="n"/>
+      <c r="E10" s="12" t="n"/>
+      <c r="F10" s="13" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>■ チーム別の報告設定（記入）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>チーム</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>報告の種類</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>内容（何を）</t>
+        </is>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
+        <is>
+          <t>タイミング（いつ）</t>
+        </is>
+      </c>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>宛先・ツール</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>(記入例)広告</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>日次数値報告</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>CPA/ROAS/消化額</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>毎日18時まで</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>Chatwork『広告』/所定シート</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="B16" s="15" t="inlineStr"/>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>完了報告</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr"/>
+      <c r="E16" s="10" t="inlineStr"/>
+      <c r="F16" s="10" t="inlineStr"/>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="B17" s="15" t="inlineStr"/>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>日次進捗報告</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr"/>
+      <c r="E17" s="10" t="inlineStr"/>
+      <c r="F17" s="10" t="inlineStr"/>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="B18" s="15" t="inlineStr"/>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>週次まとめ</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr"/>
+      <c r="E18" s="10" t="inlineStr"/>
+      <c r="F18" s="10" t="inlineStr"/>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="B19" s="15" t="inlineStr"/>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>トラブル・相談</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr"/>
+      <c r="E19" s="10" t="inlineStr"/>
+      <c r="F19" s="10" t="inlineStr"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>CSチーム</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="B21" s="15" t="inlineStr"/>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>対応件数・未完了案件</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr"/>
+      <c r="E21" s="10" t="inlineStr"/>
+      <c r="F21" s="10" t="inlineStr"/>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="B22" s="15" t="inlineStr"/>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>難対応/クレーム報告</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr"/>
+      <c r="E22" s="10" t="inlineStr"/>
+      <c r="F22" s="10" t="inlineStr"/>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="B23" s="15" t="inlineStr"/>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>返品・保証対応の共有</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr"/>
+      <c r="E23" s="10" t="inlineStr"/>
+      <c r="F23" s="10" t="inlineStr"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>LPチーム</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="B25" s="15" t="inlineStr"/>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>制作進捗報告</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr"/>
+      <c r="E25" s="10" t="inlineStr"/>
+      <c r="F25" s="10" t="inlineStr"/>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="B26" s="15" t="inlineStr"/>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>公開報告</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr"/>
+      <c r="E26" s="10" t="inlineStr"/>
+      <c r="F26" s="10" t="inlineStr"/>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="B27" s="15" t="inlineStr"/>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>数値(CVR等)報告</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr"/>
+      <c r="E27" s="10" t="inlineStr"/>
+      <c r="F27" s="10" t="inlineStr"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>広告チーム</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="B29" s="15" t="inlineStr"/>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>日次数値(CPA/ROAS/消化額)</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr"/>
+      <c r="E29" s="10" t="inlineStr"/>
+      <c r="F29" s="10" t="inlineStr"/>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="B30" s="15" t="inlineStr"/>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>施策・入稿完了報告</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr"/>
+      <c r="E30" s="10" t="inlineStr"/>
+      <c r="F30" s="10" t="inlineStr"/>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="B31" s="15" t="inlineStr"/>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>異常(CPA高騰/配信停止/審査落ち)</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr"/>
+      <c r="E31" s="10" t="inlineStr"/>
+      <c r="F31" s="10" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B9:F9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="B1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2392,6 +2769,11 @@
           <t>共通</t>
         </is>
       </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="13" t="n"/>
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="B7" s="15" t="inlineStr"/>
@@ -2447,6 +2829,11 @@
           <t>CSチーム</t>
         </is>
       </c>
+      <c r="C11" s="12" t="n"/>
+      <c r="D11" s="12" t="n"/>
+      <c r="E11" s="12" t="n"/>
+      <c r="F11" s="12" t="n"/>
+      <c r="G11" s="13" t="n"/>
     </row>
     <row r="12" ht="26" customHeight="1">
       <c r="B12" s="15" t="inlineStr"/>
@@ -2502,6 +2889,11 @@
           <t>LPチーム</t>
         </is>
       </c>
+      <c r="C16" s="12" t="n"/>
+      <c r="D16" s="12" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="12" t="n"/>
+      <c r="G16" s="13" t="n"/>
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="B17" s="15" t="inlineStr"/>
@@ -2569,6 +2961,11 @@
           <t>広告チーム</t>
         </is>
       </c>
+      <c r="C22" s="12" t="n"/>
+      <c r="D22" s="12" t="n"/>
+      <c r="E22" s="12" t="n"/>
+      <c r="F22" s="12" t="n"/>
+      <c r="G22" s="13" t="n"/>
     </row>
     <row r="23" ht="26" customHeight="1">
       <c r="B23" s="15" t="inlineStr"/>
@@ -2648,6 +3045,11 @@
           <t>SNS(参考)</t>
         </is>
       </c>
+      <c r="C29" s="12" t="n"/>
+      <c r="D29" s="12" t="n"/>
+      <c r="E29" s="12" t="n"/>
+      <c r="F29" s="12" t="n"/>
+      <c r="G29" s="13" t="n"/>
     </row>
     <row r="30" ht="26" customHeight="1">
       <c r="B30" s="15" t="inlineStr"/>
